--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819043</v>
+        <v>122819037</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498727</v>
+        <v>498735</v>
       </c>
       <c r="R2" t="n">
         <v>6911021</v>
@@ -790,7 +790,7 @@
         <v>122818863</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819037</v>
+        <v>122818967</v>
       </c>
       <c r="B4" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498735</v>
+        <v>498671</v>
       </c>
       <c r="R4" t="n">
-        <v>6911021</v>
+        <v>6910918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818967</v>
+        <v>122819043</v>
       </c>
       <c r="B5" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498671</v>
+        <v>498727</v>
       </c>
       <c r="R5" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819037</v>
+        <v>122818863</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498735</v>
+        <v>498573</v>
       </c>
       <c r="R2" t="n">
-        <v>6911021</v>
+        <v>6910818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818863</v>
+        <v>122819043</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498573</v>
+        <v>498727</v>
       </c>
       <c r="R3" t="n">
-        <v>6910818</v>
+        <v>6911021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819043</v>
+        <v>122819037</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498727</v>
+        <v>498735</v>
       </c>
       <c r="R5" t="n">
         <v>6911021</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818863</v>
+        <v>122819043</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498573</v>
+        <v>498727</v>
       </c>
       <c r="R2" t="n">
-        <v>6910818</v>
+        <v>6911021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819043</v>
+        <v>122818863</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498727</v>
+        <v>498573</v>
       </c>
       <c r="R3" t="n">
-        <v>6911021</v>
+        <v>6910818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818967</v>
+        <v>122819037</v>
       </c>
       <c r="B4" t="n">
         <v>78503</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498671</v>
+        <v>498735</v>
       </c>
       <c r="R4" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819037</v>
+        <v>122818967</v>
       </c>
       <c r="B5" t="n">
         <v>78503</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498735</v>
+        <v>498671</v>
       </c>
       <c r="R5" t="n">
-        <v>6911021</v>
+        <v>6910918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819043</v>
+        <v>122818967</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498727</v>
+        <v>498671</v>
       </c>
       <c r="R2" t="n">
-        <v>6911021</v>
+        <v>6910918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819037</v>
+        <v>122819043</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498735</v>
+        <v>498727</v>
       </c>
       <c r="R4" t="n">
         <v>6911021</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818967</v>
+        <v>122819037</v>
       </c>
       <c r="B5" t="n">
         <v>78503</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498671</v>
+        <v>498735</v>
       </c>
       <c r="R5" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818967</v>
+        <v>122819037</v>
       </c>
       <c r="B2" t="n">
         <v>78503</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498671</v>
+        <v>498735</v>
       </c>
       <c r="R2" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818863</v>
+        <v>122818967</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498573</v>
+        <v>498671</v>
       </c>
       <c r="R3" t="n">
-        <v>6910818</v>
+        <v>6910918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819043</v>
+        <v>122818863</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498727</v>
+        <v>498573</v>
       </c>
       <c r="R4" t="n">
-        <v>6911021</v>
+        <v>6910818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819037</v>
+        <v>122819043</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498735</v>
+        <v>498727</v>
       </c>
       <c r="R5" t="n">
         <v>6911021</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819037</v>
+        <v>122818863</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498735</v>
+        <v>498573</v>
       </c>
       <c r="R2" t="n">
-        <v>6911021</v>
+        <v>6910818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818967</v>
+        <v>122819037</v>
       </c>
       <c r="B3" t="n">
         <v>78503</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498671</v>
+        <v>498735</v>
       </c>
       <c r="R3" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818863</v>
+        <v>122818967</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498573</v>
+        <v>498671</v>
       </c>
       <c r="R4" t="n">
-        <v>6910818</v>
+        <v>6910918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819037</v>
+        <v>122818967</v>
       </c>
       <c r="B3" t="n">
         <v>78503</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498735</v>
+        <v>498671</v>
       </c>
       <c r="R3" t="n">
-        <v>6911021</v>
+        <v>6910918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122818967</v>
+        <v>122819043</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498671</v>
+        <v>498727</v>
       </c>
       <c r="R4" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819043</v>
+        <v>122819037</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498727</v>
+        <v>498735</v>
       </c>
       <c r="R5" t="n">
         <v>6911021</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818863</v>
+        <v>122819037</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498573</v>
+        <v>498735</v>
       </c>
       <c r="R2" t="n">
-        <v>6910818</v>
+        <v>6911021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818967</v>
+        <v>122818863</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498671</v>
+        <v>498573</v>
       </c>
       <c r="R3" t="n">
-        <v>6910918</v>
+        <v>6910818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819037</v>
+        <v>122818967</v>
       </c>
       <c r="B5" t="n">
         <v>78503</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498735</v>
+        <v>498671</v>
       </c>
       <c r="R5" t="n">
-        <v>6911021</v>
+        <v>6910918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122819037</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818863</v>
+        <v>122818967</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498573</v>
+        <v>498671</v>
       </c>
       <c r="R3" t="n">
-        <v>6910818</v>
+        <v>6910918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
         <v>122819043</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818967</v>
+        <v>122818863</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498671</v>
+        <v>498573</v>
       </c>
       <c r="R5" t="n">
-        <v>6910918</v>
+        <v>6910818</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819037</v>
+        <v>122818863</v>
       </c>
       <c r="B2" t="n">
-        <v>78506</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498735</v>
+        <v>498573</v>
       </c>
       <c r="R2" t="n">
-        <v>6911021</v>
+        <v>6910818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,7 +790,7 @@
         <v>122818967</v>
       </c>
       <c r="B3" t="n">
-        <v>78506</v>
+        <v>78508</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819043</v>
+        <v>122819037</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498727</v>
+        <v>498735</v>
       </c>
       <c r="R4" t="n">
         <v>6911021</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122818863</v>
+        <v>122819043</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498573</v>
+        <v>498727</v>
       </c>
       <c r="R5" t="n">
-        <v>6910818</v>
+        <v>6911021</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122818863</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122818967</v>
+        <v>122819037</v>
       </c>
       <c r="B3" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498671</v>
+        <v>498735</v>
       </c>
       <c r="R3" t="n">
-        <v>6910918</v>
+        <v>6911021</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819037</v>
+        <v>122818967</v>
       </c>
       <c r="B4" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498735</v>
+        <v>498671</v>
       </c>
       <c r="R4" t="n">
-        <v>6911021</v>
+        <v>6910918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
         <v>122819043</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 6292-2025 artfynd.xlsx
+++ b/artfynd/A 6292-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122818863</v>
+        <v>122819037</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498573</v>
+        <v>498735</v>
       </c>
       <c r="R2" t="n">
-        <v>6910818</v>
+        <v>6911021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819037</v>
+        <v>122819043</v>
       </c>
       <c r="B3" t="n">
-        <v>78509</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498735</v>
+        <v>498727</v>
       </c>
       <c r="R3" t="n">
         <v>6911021</v>
@@ -902,7 +902,7 @@
         <v>122818967</v>
       </c>
       <c r="B4" t="n">
-        <v>78509</v>
+        <v>78512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819043</v>
+        <v>122818863</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498727</v>
+        <v>498573</v>
       </c>
       <c r="R5" t="n">
-        <v>6911021</v>
+        <v>6910818</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
